--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J621"/>
+  <dimension ref="A1:J622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22790,6 +22790,42 @@
       <c r="J621" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="C622" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="D622" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="E622" t="n">
+        <v>345.25</v>
+      </c>
+      <c r="F622" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="G622" t="n">
+        <v>365.12</v>
+      </c>
+      <c r="H622" t="n">
+        <v>366.99</v>
+      </c>
+      <c r="I622" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B633"/>
+  <dimension ref="A1:B634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29137,6 +29173,16 @@
       </c>
       <c r="B633" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -29305,28 +29351,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2784926327990527</v>
+        <v>-0.2839051855655158</v>
       </c>
       <c r="J2" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K2" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02878901327394034</v>
+        <v>0.02989755365814695</v>
       </c>
       <c r="M2" t="n">
-        <v>10.3986848775963</v>
+        <v>10.41098728800901</v>
       </c>
       <c r="N2" t="n">
-        <v>140.5821977605453</v>
+        <v>140.7960690363402</v>
       </c>
       <c r="O2" t="n">
-        <v>11.85673638741055</v>
+        <v>11.8657519372495</v>
       </c>
       <c r="P2" t="n">
-        <v>352.2733891013413</v>
+        <v>352.3298893308237</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -29387,28 +29433,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3992936518518909</v>
+        <v>-0.4035443980986106</v>
       </c>
       <c r="J3" t="n">
+        <v>621</v>
+      </c>
+      <c r="K3" t="n">
         <v>620</v>
       </c>
-      <c r="K3" t="n">
-        <v>619</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.142365558888893</v>
+        <v>0.1447614696637975</v>
       </c>
       <c r="M3" t="n">
-        <v>6.068298944584524</v>
+        <v>6.083054728200037</v>
       </c>
       <c r="N3" t="n">
-        <v>51.46288098566747</v>
+        <v>51.65101639442213</v>
       </c>
       <c r="O3" t="n">
-        <v>7.173763376754733</v>
+        <v>7.186864155834736</v>
       </c>
       <c r="P3" t="n">
-        <v>357.6463913718927</v>
+        <v>357.6908009240112</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -29469,28 +29515,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1378727858000665</v>
+        <v>-0.1409418483723598</v>
       </c>
       <c r="J4" t="n">
+        <v>621</v>
+      </c>
+      <c r="K4" t="n">
         <v>620</v>
       </c>
-      <c r="K4" t="n">
-        <v>619</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04966495817747418</v>
+        <v>0.05160514295426355</v>
       </c>
       <c r="M4" t="n">
-        <v>3.352599579795892</v>
+        <v>3.361858791075864</v>
       </c>
       <c r="N4" t="n">
-        <v>19.48927927720548</v>
+        <v>19.59918811901235</v>
       </c>
       <c r="O4" t="n">
-        <v>4.414666383454755</v>
+        <v>4.427097030675108</v>
       </c>
       <c r="P4" t="n">
-        <v>355.4516586736643</v>
+        <v>355.4837226187573</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -29551,28 +29597,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2872152970500859</v>
+        <v>-0.2892387757449998</v>
       </c>
       <c r="J5" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K5" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2333930533214792</v>
+        <v>0.2357967948112749</v>
       </c>
       <c r="M5" t="n">
-        <v>2.832375575903</v>
+        <v>2.837316410593734</v>
       </c>
       <c r="N5" t="n">
-        <v>14.49820675321214</v>
+        <v>14.53618073701328</v>
       </c>
       <c r="O5" t="n">
-        <v>3.807651080812439</v>
+        <v>3.812634356585126</v>
       </c>
       <c r="P5" t="n">
-        <v>358.9779031389997</v>
+        <v>358.9990520054913</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -29633,28 +29679,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02722416833446257</v>
+        <v>0.02468913199309708</v>
       </c>
       <c r="J6" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K6" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004423929975077345</v>
+        <v>0.003615340647704302</v>
       </c>
       <c r="M6" t="n">
-        <v>2.174703846388383</v>
+        <v>2.184640455809039</v>
       </c>
       <c r="N6" t="n">
-        <v>8.924620933163142</v>
+        <v>9.006494307574169</v>
       </c>
       <c r="O6" t="n">
-        <v>2.987410405880508</v>
+        <v>3.00108218940671</v>
       </c>
       <c r="P6" t="n">
-        <v>364.9851899375403</v>
+        <v>365.0116854698479</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -29715,28 +29761,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03183628531440254</v>
+        <v>0.03131299401763241</v>
       </c>
       <c r="J7" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K7" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004159984168423891</v>
+        <v>0.004037976754613815</v>
       </c>
       <c r="M7" t="n">
-        <v>2.641205734453561</v>
+        <v>2.639567008839961</v>
       </c>
       <c r="N7" t="n">
-        <v>12.98246028662329</v>
+        <v>12.96565560918316</v>
       </c>
       <c r="O7" t="n">
-        <v>3.603118133870064</v>
+        <v>3.600785415597986</v>
       </c>
       <c r="P7" t="n">
-        <v>365.8805104016662</v>
+        <v>365.8859797045056</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -29797,28 +29843,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.017252334854864</v>
+        <v>-0.01794688176190124</v>
       </c>
       <c r="J8" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K8" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008853083587129218</v>
+        <v>0.0009609947217800174</v>
       </c>
       <c r="M8" t="n">
-        <v>3.238229143045652</v>
+        <v>3.236487919212194</v>
       </c>
       <c r="N8" t="n">
-        <v>17.97342604480884</v>
+        <v>17.95170789652412</v>
       </c>
       <c r="O8" t="n">
-        <v>4.239507759729759</v>
+        <v>4.23694558574029</v>
       </c>
       <c r="P8" t="n">
-        <v>369.5712882172068</v>
+        <v>369.5785474385892</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -29879,28 +29925,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02232891912620526</v>
+        <v>0.02287095222870059</v>
       </c>
       <c r="J9" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K9" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001264381447047214</v>
+        <v>0.001330893707125802</v>
       </c>
       <c r="M9" t="n">
-        <v>3.435668271369579</v>
+        <v>3.43296310242901</v>
       </c>
       <c r="N9" t="n">
-        <v>21.07279568024081</v>
+        <v>21.04326210869312</v>
       </c>
       <c r="O9" t="n">
-        <v>4.590511483510395</v>
+        <v>4.587293549435563</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9962460284199</v>
+        <v>368.9905808411622</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -29942,7 +29988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J621"/>
+  <dimension ref="A1:J622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62217,6 +62263,58 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-36.494435914068305,174.74281785737307</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-36.49495682040033,174.74219330312772</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-36.49550117067458,174.74157804301794</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-36.49607213790802,174.74100504786844</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-36.49671175626084,174.74055228488567</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-36.49740038121669,174.74027862971215</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-36.49808936453557,174.74005299163287</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>-36.49880469604945,174.73997423670883</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J622"/>
+  <dimension ref="A1:J624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22826,6 +22826,78 @@
       <c r="J622" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>334.73</v>
+      </c>
+      <c r="C623" t="n">
+        <v>340.65</v>
+      </c>
+      <c r="D623" t="n">
+        <v>344.39</v>
+      </c>
+      <c r="E623" t="n">
+        <v>345.53</v>
+      </c>
+      <c r="F623" t="n">
+        <v>357.78</v>
+      </c>
+      <c r="G623" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="H623" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="I623" t="n">
+        <v>370.69</v>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>337.05</v>
+      </c>
+      <c r="C624" t="n">
+        <v>343.03</v>
+      </c>
+      <c r="D624" t="n">
+        <v>345.66</v>
+      </c>
+      <c r="E624" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="F624" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="G624" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="H624" t="n">
+        <v>367.75</v>
+      </c>
+      <c r="I624" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B634"/>
+  <dimension ref="A1:B636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29183,6 +29255,26 @@
       </c>
       <c r="B634" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -29351,28 +29443,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2839051855655158</v>
+        <v>-0.2897254009019127</v>
       </c>
       <c r="J2" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K2" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02989755365814695</v>
+        <v>0.03125527945110751</v>
       </c>
       <c r="M2" t="n">
-        <v>10.41098728800901</v>
+        <v>10.40856814690676</v>
       </c>
       <c r="N2" t="n">
-        <v>140.7960690363402</v>
+        <v>140.6035639526958</v>
       </c>
       <c r="O2" t="n">
-        <v>11.8657519372495</v>
+        <v>11.85763736807193</v>
       </c>
       <c r="P2" t="n">
-        <v>352.3298893308237</v>
+        <v>352.3906988698</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -29433,28 +29525,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4035443980986106</v>
+        <v>-0.4069438822186491</v>
       </c>
       <c r="J3" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K3" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1447614696637975</v>
+        <v>0.1475177088166083</v>
       </c>
       <c r="M3" t="n">
-        <v>6.083054728200037</v>
+        <v>6.083045659843548</v>
       </c>
       <c r="N3" t="n">
-        <v>51.65101639442213</v>
+        <v>51.57695357155693</v>
       </c>
       <c r="O3" t="n">
-        <v>7.186864155834736</v>
+        <v>7.181709655197496</v>
       </c>
       <c r="P3" t="n">
-        <v>357.6908009240112</v>
+        <v>357.7263480303646</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -29515,28 +29607,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1409418483723598</v>
+        <v>-0.1453234335168478</v>
       </c>
       <c r="J4" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K4" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05160514295426355</v>
+        <v>0.05466588632812686</v>
       </c>
       <c r="M4" t="n">
-        <v>3.361858791075864</v>
+        <v>3.372309667838968</v>
       </c>
       <c r="N4" t="n">
-        <v>19.59918811901235</v>
+        <v>19.68274509617329</v>
       </c>
       <c r="O4" t="n">
-        <v>4.427097030675108</v>
+        <v>4.436523988008324</v>
       </c>
       <c r="P4" t="n">
-        <v>355.4837226187573</v>
+        <v>355.5295395447386</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -29597,28 +29689,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2892387757449998</v>
+        <v>-0.2926491558207861</v>
       </c>
       <c r="J5" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K5" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2357967948112749</v>
+        <v>0.2402255082125121</v>
       </c>
       <c r="M5" t="n">
-        <v>2.837316410593734</v>
+        <v>2.844310993277384</v>
       </c>
       <c r="N5" t="n">
-        <v>14.53618073701328</v>
+        <v>14.57854026018714</v>
       </c>
       <c r="O5" t="n">
-        <v>3.812634356585126</v>
+        <v>3.818185466970816</v>
       </c>
       <c r="P5" t="n">
-        <v>358.9990520054913</v>
+        <v>359.0347277597744</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -29679,28 +29771,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02468913199309708</v>
+        <v>0.01963219990577622</v>
       </c>
       <c r="J6" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K6" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003615340647704302</v>
+        <v>0.002256869240447879</v>
       </c>
       <c r="M6" t="n">
-        <v>2.184640455809039</v>
+        <v>2.204433647372024</v>
       </c>
       <c r="N6" t="n">
-        <v>9.006494307574169</v>
+        <v>9.170735874228086</v>
       </c>
       <c r="O6" t="n">
-        <v>3.00108218940671</v>
+        <v>3.028322287047415</v>
       </c>
       <c r="P6" t="n">
-        <v>365.0116854698479</v>
+        <v>365.0645860224051</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -29761,28 +29853,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03131299401763241</v>
+        <v>0.0301207444608326</v>
       </c>
       <c r="J7" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K7" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004037976754613815</v>
+        <v>0.003760786441259878</v>
       </c>
       <c r="M7" t="n">
-        <v>2.639567008839961</v>
+        <v>2.637027377372718</v>
       </c>
       <c r="N7" t="n">
-        <v>12.96565560918316</v>
+        <v>12.93511411255619</v>
       </c>
       <c r="O7" t="n">
-        <v>3.600785415597986</v>
+        <v>3.596541965910614</v>
       </c>
       <c r="P7" t="n">
-        <v>365.8859797045056</v>
+        <v>365.8984516992311</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -29843,28 +29935,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01794688176190124</v>
+        <v>-0.01895972255373989</v>
       </c>
       <c r="J8" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K8" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009609947217800174</v>
+        <v>0.001079563096050062</v>
       </c>
       <c r="M8" t="n">
-        <v>3.236487919212194</v>
+        <v>3.231136876826344</v>
       </c>
       <c r="N8" t="n">
-        <v>17.95170789652412</v>
+        <v>17.90196588678434</v>
       </c>
       <c r="O8" t="n">
-        <v>4.23694558574029</v>
+        <v>4.23107148211707</v>
       </c>
       <c r="P8" t="n">
-        <v>369.5785474385892</v>
+        <v>369.5891426857542</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -29925,28 +30017,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02287095222870059</v>
+        <v>0.02357544630502481</v>
       </c>
       <c r="J9" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K9" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001330893707125802</v>
+        <v>0.001423838444110426</v>
       </c>
       <c r="M9" t="n">
-        <v>3.43296310242901</v>
+        <v>3.425598725192475</v>
       </c>
       <c r="N9" t="n">
-        <v>21.04326210869312</v>
+        <v>20.97945619719858</v>
       </c>
       <c r="O9" t="n">
-        <v>4.587293549435563</v>
+        <v>4.580333633830463</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9905808411622</v>
+        <v>368.9832111303396</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -29988,7 +30080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J622"/>
+  <dimension ref="A1:J624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62315,6 +62407,110 @@
         </is>
       </c>
     </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-36.49447786351276,174.74286574243382</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-36.49499983033843,174.74224239868562</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-36.495513313959215,174.74159377773003</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-36.49607372263608,174.74100748017702</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-36.49671099361263,174.74055063906414</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-36.49739871152403,174.7402724945889</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>-36.498089984551484,174.7400568223532</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>-36.498804059114384,174.7399681480777</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-36.49449323834342,174.74288329273762</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-36.49501560285259,174.74226040292544</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-36.495521222661324,174.74160402546823</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-36.49608062752203,174.74101807809413</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-36.49671175626084,174.74055228488567</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-36.4974006115191,174.74027947593606</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>-36.498090710855685,174.74006130976858</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>-36.49880403595309,174.73996792667296</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J624"/>
+  <dimension ref="A1:J626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22896,6 +22896,78 @@
         <v>370.67</v>
       </c>
       <c r="J624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>340.09</v>
+      </c>
+      <c r="C625" t="n">
+        <v>345</v>
+      </c>
+      <c r="D625" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="E625" t="n">
+        <v>347.61</v>
+      </c>
+      <c r="F625" t="n">
+        <v>358.95</v>
+      </c>
+      <c r="G625" t="n">
+        <v>364.97</v>
+      </c>
+      <c r="H625" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="I625" t="n">
+        <v>371.09</v>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>341.56</v>
+      </c>
+      <c r="C626" t="n">
+        <v>346.23</v>
+      </c>
+      <c r="D626" t="n">
+        <v>346.98</v>
+      </c>
+      <c r="E626" t="n">
+        <v>348.44</v>
+      </c>
+      <c r="F626" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="G626" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="H626" t="n">
+        <v>368.08</v>
+      </c>
+      <c r="I626" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="J626" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22912,7 +22984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B636"/>
+  <dimension ref="A1:B638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29275,6 +29347,26 @@
       </c>
       <c r="B636" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -29443,28 +29535,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2897254009019127</v>
+        <v>-0.2922628925911711</v>
       </c>
       <c r="J2" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K2" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03125527945110751</v>
+        <v>0.03199550813081187</v>
       </c>
       <c r="M2" t="n">
-        <v>10.40856814690676</v>
+        <v>10.3885468914773</v>
       </c>
       <c r="N2" t="n">
-        <v>140.6035639526958</v>
+        <v>140.2022990738029</v>
       </c>
       <c r="O2" t="n">
-        <v>11.85763736807193</v>
+        <v>11.8407051763737</v>
       </c>
       <c r="P2" t="n">
-        <v>352.3906988698</v>
+        <v>352.4172984433067</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -29525,28 +29617,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4069438822186491</v>
+        <v>-0.4078364624456197</v>
       </c>
       <c r="J3" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K3" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1475177088166083</v>
+        <v>0.1489498412844894</v>
       </c>
       <c r="M3" t="n">
-        <v>6.083045659843548</v>
+        <v>6.068651612412706</v>
       </c>
       <c r="N3" t="n">
-        <v>51.57695357155693</v>
+        <v>51.41892692651991</v>
       </c>
       <c r="O3" t="n">
-        <v>7.181709655197496</v>
+        <v>7.170699193699308</v>
       </c>
       <c r="P3" t="n">
-        <v>357.7263480303646</v>
+        <v>357.7357110767341</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -29607,28 +29699,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1453234335168478</v>
+        <v>-0.1485237253532904</v>
       </c>
       <c r="J4" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K4" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05466588632812686</v>
+        <v>0.05713025627433277</v>
       </c>
       <c r="M4" t="n">
-        <v>3.372309667838968</v>
+        <v>3.377123529938193</v>
       </c>
       <c r="N4" t="n">
-        <v>19.68274509617329</v>
+        <v>19.69758529709865</v>
       </c>
       <c r="O4" t="n">
-        <v>4.436523988008324</v>
+        <v>4.438196176049302</v>
       </c>
       <c r="P4" t="n">
-        <v>355.5295395447386</v>
+        <v>355.5631165701542</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -29689,28 +29781,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2926491558207861</v>
+        <v>-0.294777191598774</v>
       </c>
       <c r="J5" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K5" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2402255082125121</v>
+        <v>0.2437473986847646</v>
       </c>
       <c r="M5" t="n">
-        <v>2.844310993277384</v>
+        <v>2.845238359099036</v>
       </c>
       <c r="N5" t="n">
-        <v>14.57854026018714</v>
+        <v>14.56676088724037</v>
       </c>
       <c r="O5" t="n">
-        <v>3.818185466970816</v>
+        <v>3.81664261979562</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0347277597744</v>
+        <v>359.0570628501372</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -29771,28 +29863,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01963219990577622</v>
+        <v>0.01549425582803969</v>
       </c>
       <c r="J6" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K6" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002256869240447879</v>
+        <v>0.001397147835800583</v>
       </c>
       <c r="M6" t="n">
-        <v>2.204433647372024</v>
+        <v>2.219344861305526</v>
       </c>
       <c r="N6" t="n">
-        <v>9.170735874228086</v>
+        <v>9.271291373178126</v>
       </c>
       <c r="O6" t="n">
-        <v>3.028322287047415</v>
+        <v>3.044879533442682</v>
       </c>
       <c r="P6" t="n">
-        <v>365.0645860224051</v>
+        <v>365.1080182335699</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -29853,28 +29945,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0301207444608326</v>
+        <v>0.0292190430668104</v>
       </c>
       <c r="J7" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K7" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003760786441259878</v>
+        <v>0.003563140656424824</v>
       </c>
       <c r="M7" t="n">
-        <v>2.637027377372718</v>
+        <v>2.63305807773498</v>
       </c>
       <c r="N7" t="n">
-        <v>12.93511411255619</v>
+        <v>12.90022069391055</v>
       </c>
       <c r="O7" t="n">
-        <v>3.596541965910614</v>
+        <v>3.59168772221508</v>
       </c>
       <c r="P7" t="n">
-        <v>365.8984516992311</v>
+        <v>365.9079151554217</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -29935,28 +30027,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01895972255373989</v>
+        <v>-0.01973289044642496</v>
       </c>
       <c r="J8" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K8" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001079563096050062</v>
+        <v>0.001177325184565592</v>
       </c>
       <c r="M8" t="n">
-        <v>3.231136876826344</v>
+        <v>3.224603365677194</v>
       </c>
       <c r="N8" t="n">
-        <v>17.90196588678434</v>
+        <v>17.8493215676006</v>
       </c>
       <c r="O8" t="n">
-        <v>4.23107148211707</v>
+        <v>4.224845744829106</v>
       </c>
       <c r="P8" t="n">
-        <v>369.5891426857542</v>
+        <v>369.5972574610631</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -30017,28 +30109,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02357544630502481</v>
+        <v>0.02462878629386447</v>
       </c>
       <c r="J9" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K9" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001423838444110426</v>
+        <v>0.001564142570086857</v>
       </c>
       <c r="M9" t="n">
-        <v>3.425598725192475</v>
+        <v>3.420066200751842</v>
       </c>
       <c r="N9" t="n">
-        <v>20.97945619719858</v>
+        <v>20.92079576766058</v>
       </c>
       <c r="O9" t="n">
-        <v>4.580333633830463</v>
+        <v>4.573925640810154</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9832111303396</v>
+        <v>368.9721545207952</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -30080,7 +30172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J624"/>
+  <dimension ref="A1:J626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62511,6 +62603,110 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-36.49451338466897,174.74290628969797</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-36.495028658250725,174.74227530560006</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-36.49552657815987,174.74161096488265</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-36.49608549490005,174.74102554875813</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-36.49671624242616,174.7405619661894</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-36.49739994939966,174.7402770430423</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>-36.49809063999674,174.74006087197196</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>-36.498804522339896,174.73997257617307</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-36.494523126476,174.74291740994292</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-36.495036809589664,174.74228461031822</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-36.49552944272867,174.7416146766629</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-36.496090192485326,174.74103275881845</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-36.49671830606192,174.7405664195895</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-36.49740182060665,174.74028391861168</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>-36.49809129544186,174.74006492159077</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>-36.4988048581783,174.7399757865422</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J626"/>
+  <dimension ref="A1:J628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22970,6 +22970,78 @@
       <c r="J626" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>356.36</v>
+      </c>
+      <c r="C627" t="n">
+        <v>355.62</v>
+      </c>
+      <c r="D627" t="n">
+        <v>351.61</v>
+      </c>
+      <c r="E627" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="F627" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="G627" t="n">
+        <v>366.55</v>
+      </c>
+      <c r="H627" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="I627" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="C628" t="n">
+        <v>355.89</v>
+      </c>
+      <c r="D628" t="n">
+        <v>351.93</v>
+      </c>
+      <c r="E628" t="n">
+        <v>352.65</v>
+      </c>
+      <c r="F628" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="G628" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="H628" t="n">
+        <v>369.11</v>
+      </c>
+      <c r="I628" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -22984,7 +23056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B638"/>
+  <dimension ref="A1:B640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29367,6 +29439,26 @@
       </c>
       <c r="B638" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -29535,34 +29627,30 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2922628925911711</v>
+        <v>-0.284764102860431</v>
       </c>
       <c r="J2" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K2" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03199550813081187</v>
+        <v>0.03054477962370927</v>
       </c>
       <c r="M2" t="n">
-        <v>10.3885468914773</v>
+        <v>10.38969862803747</v>
       </c>
       <c r="N2" t="n">
-        <v>140.2022990738029</v>
+        <v>140.1803852803394</v>
       </c>
       <c r="O2" t="n">
-        <v>11.8407051763737</v>
+        <v>11.83977978175014</v>
       </c>
       <c r="P2" t="n">
-        <v>352.4172984433067</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>352.338313586035</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.7403336545289 -36.49225955088011, 174.74730184994155 -36.49836380358923)</t>
@@ -29617,34 +29705,30 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4078364624456197</v>
+        <v>-0.4021379166546994</v>
       </c>
       <c r="J3" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K3" t="n">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1489498412844894</v>
+        <v>0.1457112638247746</v>
       </c>
       <c r="M3" t="n">
-        <v>6.068651612412706</v>
+        <v>6.072979771345574</v>
       </c>
       <c r="N3" t="n">
-        <v>51.41892692651991</v>
+        <v>51.50058182804937</v>
       </c>
       <c r="O3" t="n">
-        <v>7.170699193699308</v>
+        <v>7.176390584970231</v>
       </c>
       <c r="P3" t="n">
-        <v>357.7357110767341</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>357.675640213033</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.73966552286367 -36.49274227594311, 174.74663371469435 -36.498846540691964)</t>
@@ -29699,34 +29783,30 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1485237253532904</v>
+        <v>-0.1484342618166196</v>
       </c>
       <c r="J4" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K4" t="n">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05713025627433277</v>
+        <v>0.05745085231450631</v>
       </c>
       <c r="M4" t="n">
-        <v>3.377123529938193</v>
+        <v>3.366849433379294</v>
       </c>
       <c r="N4" t="n">
-        <v>19.69758529709865</v>
+        <v>19.63479521381605</v>
       </c>
       <c r="O4" t="n">
-        <v>4.438196176049302</v>
+        <v>4.431116700541303</v>
       </c>
       <c r="P4" t="n">
-        <v>355.5631165701542</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>355.5621729956476</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.7388149423126 -36.49336865074575, 174.7462483243012 -36.499105202091826)</t>
@@ -29781,34 +29861,30 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.294777191598774</v>
+        <v>-0.2938380720203986</v>
       </c>
       <c r="J5" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K5" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2437473986847646</v>
+        <v>0.2438047404549931</v>
       </c>
       <c r="M5" t="n">
-        <v>2.845238359099036</v>
+        <v>2.840934193192116</v>
       </c>
       <c r="N5" t="n">
-        <v>14.56676088724037</v>
+        <v>14.52697173082922</v>
       </c>
       <c r="O5" t="n">
-        <v>3.81664261979562</v>
+        <v>3.811426469293252</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0570628501372</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>359.0471596230423</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.73800599943112 -36.49411807153893, 174.74600942071103 -36.49933240225918)</t>
@@ -29863,34 +29939,30 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01549425582803969</v>
+        <v>0.01407123815867675</v>
       </c>
       <c r="J6" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K6" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001397147835800583</v>
+        <v>0.001158929036896739</v>
       </c>
       <c r="M6" t="n">
-        <v>2.219344861305526</v>
+        <v>2.219867238820296</v>
       </c>
       <c r="N6" t="n">
-        <v>9.271291373178126</v>
+        <v>9.257022719603864</v>
       </c>
       <c r="O6" t="n">
-        <v>3.044879533442682</v>
+        <v>3.042535574090115</v>
       </c>
       <c r="P6" t="n">
-        <v>365.1080182335699</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>365.1230244756089</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.73708693261204 -36.49510588076084, 174.74600852791653 -36.49923988390902)</t>
@@ -29945,34 +30017,30 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0292190430668104</v>
+        <v>0.0290350019476576</v>
       </c>
       <c r="J7" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K7" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003563140656424824</v>
+        <v>0.003543630013364996</v>
       </c>
       <c r="M7" t="n">
-        <v>2.63305807773498</v>
+        <v>2.625557899966243</v>
       </c>
       <c r="N7" t="n">
-        <v>12.90022069391055</v>
+        <v>12.85940251256636</v>
       </c>
       <c r="O7" t="n">
-        <v>3.59168772221508</v>
+        <v>3.586000908054313</v>
       </c>
       <c r="P7" t="n">
-        <v>365.9079151554217</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>365.9098564338022</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.73641651372307 -36.49634921697812, 174.74616635612887 -36.49900256346259)</t>
@@ -30027,34 +30095,30 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01973289044642496</v>
+        <v>-0.01959188608630606</v>
       </c>
       <c r="J8" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K8" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001177325184565592</v>
+        <v>0.001168883686892275</v>
       </c>
       <c r="M8" t="n">
-        <v>3.224603365677194</v>
+        <v>3.215011000163745</v>
       </c>
       <c r="N8" t="n">
-        <v>17.8493215676006</v>
+        <v>17.79264094091867</v>
       </c>
       <c r="O8" t="n">
-        <v>4.224845744829106</v>
+        <v>4.218132399643078</v>
       </c>
       <c r="P8" t="n">
-        <v>369.5972574610631</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>369.595771086398</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.7360363481129 -36.497439182630494, 174.74612550155624 -36.49907205407805)</t>
@@ -30109,34 +30173,30 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02462878629386447</v>
+        <v>0.02603369334139611</v>
       </c>
       <c r="J9" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K9" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001564142570086857</v>
+        <v>0.001758624420100552</v>
       </c>
       <c r="M9" t="n">
-        <v>3.420066200751842</v>
+        <v>3.416396426491543</v>
       </c>
       <c r="N9" t="n">
-        <v>20.92079576766058</v>
+        <v>20.86897851702981</v>
       </c>
       <c r="O9" t="n">
-        <v>4.573925640810154</v>
+        <v>4.56825771131947</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9721545207952</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>368.9573391895452</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.73586454126354 -36.49837470512503, 174.74606952435937 -36.49944216555688)</t>
@@ -30172,7 +30232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J626"/>
+  <dimension ref="A1:J628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62707,6 +62767,110 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-36.494621207191315,174.74302936902765</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-36.495099038077946,174.74235564396298</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-36.49555827522952,174.7416520365529</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-36.4961146991577,174.74107037276164</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-36.49673571237417,174.74060398306037</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-36.49740449787131,174.74029375596535</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>-36.49809375778849,174.74008013502416</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>-36.49880534456481,174.7399804360424</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-36.49462027940131,174.74302830995393</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-36.49510082739482,174.74235768646562</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-36.495560267972095,174.74165461866292</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-36.496114019989136,174.74106933034258</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-36.49673593668223,174.74060446712582</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>-36.497403605449854,174.7402904768474</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>-36.49809312005862,174.74007619485425</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>-36.49880534456481,174.7399804360424</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J628"/>
+  <dimension ref="A1:J629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23042,6 +23042,42 @@
       <c r="J628" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>356.58</v>
+      </c>
+      <c r="C629" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="D629" t="n">
+        <v>351.77</v>
+      </c>
+      <c r="E629" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="F629" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="G629" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="H629" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="I629" t="n">
+        <v>371.56</v>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23056,7 +23092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B640"/>
+  <dimension ref="A1:B641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29459,6 +29495,16 @@
       </c>
       <c r="B640" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -29627,28 +29673,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.284764102860431</v>
+        <v>-0.2809641096871252</v>
       </c>
       <c r="J2" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K2" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03054477962370927</v>
+        <v>0.02981620178106925</v>
       </c>
       <c r="M2" t="n">
-        <v>10.38969862803747</v>
+        <v>10.3904532991175</v>
       </c>
       <c r="N2" t="n">
-        <v>140.1803852803394</v>
+        <v>140.1773680231138</v>
       </c>
       <c r="O2" t="n">
-        <v>11.83977978175014</v>
+        <v>11.83965236073736</v>
       </c>
       <c r="P2" t="n">
-        <v>352.338313586035</v>
+        <v>352.2982318403452</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29705,28 +29751,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4021379166546994</v>
+        <v>-0.3992728254804063</v>
       </c>
       <c r="J3" t="n">
+        <v>628</v>
+      </c>
+      <c r="K3" t="n">
         <v>627</v>
       </c>
-      <c r="K3" t="n">
-        <v>626</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1457112638247746</v>
+        <v>0.1440789005883261</v>
       </c>
       <c r="M3" t="n">
-        <v>6.072979771345574</v>
+        <v>6.0751826220246</v>
       </c>
       <c r="N3" t="n">
-        <v>51.50058182804937</v>
+        <v>51.54374239072528</v>
       </c>
       <c r="O3" t="n">
-        <v>7.176390584970231</v>
+        <v>7.179397077103709</v>
       </c>
       <c r="P3" t="n">
-        <v>357.675640213033</v>
+        <v>357.6453960257542</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29783,28 +29829,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1484342618166196</v>
+        <v>-0.1483887166564083</v>
       </c>
       <c r="J4" t="n">
+        <v>628</v>
+      </c>
+      <c r="K4" t="n">
         <v>627</v>
       </c>
-      <c r="K4" t="n">
-        <v>626</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05745085231450631</v>
+        <v>0.05761047212815829</v>
       </c>
       <c r="M4" t="n">
-        <v>3.366849433379294</v>
+        <v>3.361707154735105</v>
       </c>
       <c r="N4" t="n">
-        <v>19.63479521381605</v>
+        <v>19.60351141409444</v>
       </c>
       <c r="O4" t="n">
-        <v>4.431116700541303</v>
+        <v>4.427585280273486</v>
       </c>
       <c r="P4" t="n">
-        <v>355.5621729956476</v>
+        <v>355.5616922164084</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29861,28 +29907,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2938380720203986</v>
+        <v>-0.2933822447357317</v>
       </c>
       <c r="J5" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K5" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2438047404549931</v>
+        <v>0.2438486567259072</v>
       </c>
       <c r="M5" t="n">
-        <v>2.840934193192116</v>
+        <v>2.838747151059498</v>
       </c>
       <c r="N5" t="n">
-        <v>14.52697173082922</v>
+        <v>14.50700501052276</v>
       </c>
       <c r="O5" t="n">
-        <v>3.811426469293252</v>
+        <v>3.808806244812508</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0471596230423</v>
+        <v>359.0423460297749</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29939,28 +29985,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01407123815867675</v>
+        <v>0.01335208550981413</v>
       </c>
       <c r="J6" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K6" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001158929036896739</v>
+        <v>0.001046443901804195</v>
       </c>
       <c r="M6" t="n">
-        <v>2.219867238820296</v>
+        <v>2.220183911496423</v>
       </c>
       <c r="N6" t="n">
-        <v>9.257022719603864</v>
+        <v>9.25016122070509</v>
       </c>
       <c r="O6" t="n">
-        <v>3.042535574090115</v>
+        <v>3.041407769554272</v>
       </c>
       <c r="P6" t="n">
-        <v>365.1230244756089</v>
+        <v>365.130618817732</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30017,28 +30063,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0290350019476576</v>
+        <v>0.02886024582336776</v>
       </c>
       <c r="J7" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K7" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003543630013364996</v>
+        <v>0.00351357122315854</v>
       </c>
       <c r="M7" t="n">
-        <v>2.625557899966243</v>
+        <v>2.622226831642981</v>
       </c>
       <c r="N7" t="n">
-        <v>12.85940251256636</v>
+        <v>12.83939101386071</v>
       </c>
       <c r="O7" t="n">
-        <v>3.586000908054313</v>
+        <v>3.583209596696893</v>
       </c>
       <c r="P7" t="n">
-        <v>365.9098564338022</v>
+        <v>365.9117018803817</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30095,28 +30141,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01959188608630606</v>
+        <v>-0.01977631852436131</v>
       </c>
       <c r="J8" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K8" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001168883686892275</v>
+        <v>0.001195177182452878</v>
       </c>
       <c r="M8" t="n">
-        <v>3.215011000163745</v>
+        <v>3.210801338975684</v>
       </c>
       <c r="N8" t="n">
-        <v>17.79264094091867</v>
+        <v>17.76482691633553</v>
       </c>
       <c r="O8" t="n">
-        <v>4.218132399643078</v>
+        <v>4.21483415051358</v>
       </c>
       <c r="P8" t="n">
-        <v>369.595771086398</v>
+        <v>369.597718716064</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30173,28 +30219,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02603369334139611</v>
+        <v>0.02665077938418697</v>
       </c>
       <c r="J9" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K9" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001758624420100552</v>
+        <v>0.001848876419111467</v>
       </c>
       <c r="M9" t="n">
-        <v>3.416396426491543</v>
+        <v>3.414121999087373</v>
       </c>
       <c r="N9" t="n">
-        <v>20.86897851702981</v>
+        <v>20.84154888104175</v>
       </c>
       <c r="O9" t="n">
-        <v>4.56825771131947</v>
+        <v>4.56525452532953</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9573391895452</v>
+        <v>368.950822683577</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30232,7 +30278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J628"/>
+  <dimension ref="A1:J629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62871,6 +62917,58 @@
         </is>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-36.49462266514704,174.74303103328646</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-36.49510089366583,174.74235776211387</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-36.49555927160081,174.74165332760788</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-36.4961141331839,174.7410695040791</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-36.49673562265093,174.7406037894342</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>-36.497403317571944,174.74028941906744</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>-36.49809203946047,174.74006951845544</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>-36.49880506662969,174.73997777918515</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J629"/>
+  <dimension ref="A1:J632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23078,6 +23078,114 @@
       <c r="J629" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>355.87</v>
+      </c>
+      <c r="C630" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="D630" t="n">
+        <v>350.87</v>
+      </c>
+      <c r="E630" t="n">
+        <v>351.91</v>
+      </c>
+      <c r="F630" t="n">
+        <v>363.08</v>
+      </c>
+      <c r="G630" t="n">
+        <v>365.24</v>
+      </c>
+      <c r="H630" t="n">
+        <v>366.61</v>
+      </c>
+      <c r="I630" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="C631" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="D631" t="n">
+        <v>351.05</v>
+      </c>
+      <c r="E631" t="n">
+        <v>351.53</v>
+      </c>
+      <c r="F631" t="n">
+        <v>362.76</v>
+      </c>
+      <c r="G631" t="n">
+        <v>364.79</v>
+      </c>
+      <c r="H631" t="n">
+        <v>366.77</v>
+      </c>
+      <c r="I631" t="n">
+        <v>368.9</v>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="C632" t="n">
+        <v>356.38</v>
+      </c>
+      <c r="D632" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="E632" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="F632" t="n">
+        <v>362.79</v>
+      </c>
+      <c r="G632" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="H632" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="I632" t="n">
+        <v>369.06</v>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23092,7 +23200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B641"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29505,6 +29613,36 @@
       </c>
       <c r="B641" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -29673,28 +29811,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2809641096871252</v>
+        <v>-0.2703537394582209</v>
       </c>
       <c r="J2" t="n">
+        <v>631</v>
+      </c>
+      <c r="K2" t="n">
         <v>628</v>
       </c>
-      <c r="K2" t="n">
-        <v>625</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02981620178106925</v>
+        <v>0.02784472145986749</v>
       </c>
       <c r="M2" t="n">
-        <v>10.3904532991175</v>
+        <v>10.38902092285411</v>
       </c>
       <c r="N2" t="n">
-        <v>140.1773680231138</v>
+        <v>140.0836914942582</v>
       </c>
       <c r="O2" t="n">
-        <v>11.83965236073736</v>
+        <v>11.83569564893666</v>
       </c>
       <c r="P2" t="n">
-        <v>352.2982318403452</v>
+        <v>352.1859409852354</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29751,28 +29889,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3992728254804063</v>
+        <v>-0.3902641404791689</v>
       </c>
       <c r="J3" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K3" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1440789005883261</v>
+        <v>0.1388569317700138</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0751826220246</v>
+        <v>6.083272431657748</v>
       </c>
       <c r="N3" t="n">
-        <v>51.54374239072528</v>
+        <v>51.71253504858232</v>
       </c>
       <c r="O3" t="n">
-        <v>7.179397077103709</v>
+        <v>7.191142819370389</v>
       </c>
       <c r="P3" t="n">
-        <v>357.6453960257542</v>
+        <v>357.549982776142</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29829,28 +29967,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1483887166564083</v>
+        <v>-0.1491220586013927</v>
       </c>
       <c r="J4" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K4" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05761047212815829</v>
+        <v>0.05872796959288828</v>
       </c>
       <c r="M4" t="n">
-        <v>3.361707154735105</v>
+        <v>3.349246877171526</v>
       </c>
       <c r="N4" t="n">
-        <v>19.60351141409444</v>
+        <v>19.51303105494056</v>
       </c>
       <c r="O4" t="n">
-        <v>4.427585280273486</v>
+        <v>4.417355663170055</v>
       </c>
       <c r="P4" t="n">
-        <v>355.5616922164084</v>
+        <v>355.5694611392393</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29907,28 +30045,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2933822447357317</v>
+        <v>-0.2929703092563058</v>
       </c>
       <c r="J5" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K5" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2438486567259072</v>
+        <v>0.245292212489859</v>
       </c>
       <c r="M5" t="n">
-        <v>2.838747151059498</v>
+        <v>2.827339184007908</v>
       </c>
       <c r="N5" t="n">
-        <v>14.50700501052276</v>
+        <v>14.43902260093046</v>
       </c>
       <c r="O5" t="n">
-        <v>3.808806244812508</v>
+        <v>3.799871392682975</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0423460297749</v>
+        <v>359.0379829270026</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29985,28 +30123,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01335208550981413</v>
+        <v>0.01085045543860555</v>
       </c>
       <c r="J6" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K6" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001046443901804195</v>
+        <v>0.0006963151366168319</v>
       </c>
       <c r="M6" t="n">
-        <v>2.220183911496423</v>
+        <v>2.222872896876954</v>
       </c>
       <c r="N6" t="n">
-        <v>9.25016122070509</v>
+        <v>9.23810926396256</v>
       </c>
       <c r="O6" t="n">
-        <v>3.041407769554272</v>
+        <v>3.039425811557598</v>
       </c>
       <c r="P6" t="n">
-        <v>365.130618817732</v>
+        <v>365.157125235629</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30063,28 +30201,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02886024582336776</v>
+        <v>0.02712890735451604</v>
       </c>
       <c r="J7" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K7" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00351357122315854</v>
+        <v>0.003135393602215375</v>
       </c>
       <c r="M7" t="n">
-        <v>2.622226831642981</v>
+        <v>2.618069492969334</v>
       </c>
       <c r="N7" t="n">
-        <v>12.83939101386071</v>
+        <v>12.79393736130389</v>
       </c>
       <c r="O7" t="n">
-        <v>3.583209596696893</v>
+        <v>3.576861384133286</v>
       </c>
       <c r="P7" t="n">
-        <v>365.9117018803817</v>
+        <v>365.9300492369431</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30141,28 +30279,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01977631852436131</v>
+        <v>-0.02212666280550101</v>
       </c>
       <c r="J8" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K8" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001195177182452878</v>
+        <v>0.001509346586901161</v>
       </c>
       <c r="M8" t="n">
-        <v>3.210801338975684</v>
+        <v>3.206987329502361</v>
       </c>
       <c r="N8" t="n">
-        <v>17.76482691633553</v>
+        <v>17.70852416332872</v>
       </c>
       <c r="O8" t="n">
-        <v>4.21483415051358</v>
+        <v>4.208149731571908</v>
       </c>
       <c r="P8" t="n">
-        <v>369.597718716064</v>
+        <v>369.6226221006154</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30219,28 +30357,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02665077938418697</v>
+        <v>0.02635688746421634</v>
       </c>
       <c r="J9" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K9" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001848876419111467</v>
+        <v>0.001827645369851361</v>
       </c>
       <c r="M9" t="n">
-        <v>3.414121999087373</v>
+        <v>3.400668341480368</v>
       </c>
       <c r="N9" t="n">
-        <v>20.84154888104175</v>
+        <v>20.74423185616315</v>
       </c>
       <c r="O9" t="n">
-        <v>4.56525452532953</v>
+        <v>4.554583609526029</v>
       </c>
       <c r="P9" t="n">
-        <v>368.950822683577</v>
+        <v>368.9539413205054</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30278,7 +30416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J629"/>
+  <dimension ref="A1:J632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62969,6 +63107,162 @@
         </is>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-36.494617959926224,174.74302566226964</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-36.49510149010477,174.74235844294813</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-36.49555366701208,174.7416460654239</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-36.49610983178267,174.74106290209207</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-36.49673477028026,174.7406019499855</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>-36.4974007266703,174.740279899048</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>-36.4980886913753,174.74004883256507</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>-36.49880337585641,174.73996161663717</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-36.494617827384786,174.7430255109734</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-36.49510752076502,174.74236532693936</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-36.49555478792987,174.7416475178606</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-36.49610768108192,174.74105960109884</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-36.49673333470852,174.74059885196672</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>-36.49739943121918,174.74027513903854</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>-36.49808897481122,174.7400505837515</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>-36.498801986178094,174.73994833235162</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-36.494618622633396,174.74302641875084</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-36.4951040746735,174.74236139322997</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-36.495552234728216,174.74164420953258</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-36.49610796406887,174.74106003544006</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-36.496733469293375,174.74059914240598</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-36.497398884250885,174.74027312925682</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>-36.498088461083576,174.74004740972615</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>-36.49880217146863,174.73995010358968</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J632"/>
+  <dimension ref="A1:J636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23186,6 +23186,150 @@
       <c r="J632" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>354.68</v>
+      </c>
+      <c r="C633" t="n">
+        <v>355.53</v>
+      </c>
+      <c r="D633" t="n">
+        <v>350.38</v>
+      </c>
+      <c r="E633" t="n">
+        <v>350.91</v>
+      </c>
+      <c r="F633" t="n">
+        <v>362</v>
+      </c>
+      <c r="G633" t="n">
+        <v>364.46</v>
+      </c>
+      <c r="H633" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="I633" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="C634" t="n">
+        <v>353.88</v>
+      </c>
+      <c r="D634" t="n">
+        <v>349.43</v>
+      </c>
+      <c r="E634" t="n">
+        <v>349.92</v>
+      </c>
+      <c r="F634" t="n">
+        <v>361.28</v>
+      </c>
+      <c r="G634" t="n">
+        <v>363.97</v>
+      </c>
+      <c r="H634" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="I634" t="n">
+        <v>368.22</v>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>349.12</v>
+      </c>
+      <c r="C635" t="n">
+        <v>351.9</v>
+      </c>
+      <c r="D635" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="E635" t="n">
+        <v>349.91</v>
+      </c>
+      <c r="F635" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="G635" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="H635" t="n">
+        <v>365.43</v>
+      </c>
+      <c r="I635" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>346.66</v>
+      </c>
+      <c r="C636" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="D636" t="n">
+        <v>348.39</v>
+      </c>
+      <c r="E636" t="n">
+        <v>349.34</v>
+      </c>
+      <c r="F636" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="G636" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="H636" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="I636" t="n">
+        <v>367.38</v>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23200,7 +23344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29643,6 +29787,46 @@
       </c>
       <c r="B644" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -29811,28 +29995,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2703537394582209</v>
+        <v>-0.263095707597757</v>
       </c>
       <c r="J2" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K2" t="n">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02784472145986749</v>
+        <v>0.02672647386977556</v>
       </c>
       <c r="M2" t="n">
-        <v>10.38902092285411</v>
+        <v>10.35580292915879</v>
       </c>
       <c r="N2" t="n">
-        <v>140.0836914942582</v>
+        <v>139.4607501932479</v>
       </c>
       <c r="O2" t="n">
-        <v>11.83569564893666</v>
+        <v>11.80935011731162</v>
       </c>
       <c r="P2" t="n">
-        <v>352.1859409852354</v>
+        <v>352.1088172265488</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29889,28 +30073,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3902641404791689</v>
+        <v>-0.3830516342240334</v>
       </c>
       <c r="J3" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K3" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1388569317700138</v>
+        <v>0.13559725363151</v>
       </c>
       <c r="M3" t="n">
-        <v>6.083272431657748</v>
+        <v>6.074160982956466</v>
       </c>
       <c r="N3" t="n">
-        <v>51.71253504858232</v>
+        <v>51.61404948183907</v>
       </c>
       <c r="O3" t="n">
-        <v>7.191142819370389</v>
+        <v>7.184291856671684</v>
       </c>
       <c r="P3" t="n">
-        <v>357.549982776142</v>
+        <v>357.4732696218333</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29967,28 +30151,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1491220586013927</v>
+        <v>-0.1520432177786217</v>
       </c>
       <c r="J4" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K4" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05872796959288828</v>
+        <v>0.06161900061929859</v>
       </c>
       <c r="M4" t="n">
-        <v>3.349246877171526</v>
+        <v>3.342238895596934</v>
       </c>
       <c r="N4" t="n">
-        <v>19.51303105494056</v>
+        <v>19.42614874838375</v>
       </c>
       <c r="O4" t="n">
-        <v>4.417355663170055</v>
+        <v>4.407510493281185</v>
       </c>
       <c r="P4" t="n">
-        <v>355.5694611392393</v>
+        <v>355.6005556683036</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30045,28 +30229,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2929703092563058</v>
+        <v>-0.2944851390546526</v>
       </c>
       <c r="J5" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K5" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L5" t="n">
-        <v>0.245292212489859</v>
+        <v>0.2497191605575398</v>
       </c>
       <c r="M5" t="n">
-        <v>2.827339184007908</v>
+        <v>2.816779942110757</v>
       </c>
       <c r="N5" t="n">
-        <v>14.43902260093046</v>
+        <v>14.35884687231257</v>
       </c>
       <c r="O5" t="n">
-        <v>3.799871392682975</v>
+        <v>3.789306911865621</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0379829270026</v>
+        <v>359.0541153495346</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30123,28 +30307,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01085045543860555</v>
+        <v>0.005243455151492933</v>
       </c>
       <c r="J6" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K6" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006963151366168319</v>
+        <v>0.0001628247127638538</v>
       </c>
       <c r="M6" t="n">
-        <v>2.222872896876954</v>
+        <v>2.238528954533635</v>
       </c>
       <c r="N6" t="n">
-        <v>9.23810926396256</v>
+        <v>9.303896771297808</v>
       </c>
       <c r="O6" t="n">
-        <v>3.039425811557598</v>
+        <v>3.050228970306624</v>
       </c>
       <c r="P6" t="n">
-        <v>365.157125235629</v>
+        <v>365.2168201187923</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30201,28 +30385,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02712890735451604</v>
+        <v>0.02396565625825717</v>
       </c>
       <c r="J7" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K7" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003135393602215375</v>
+        <v>0.002475943846454443</v>
       </c>
       <c r="M7" t="n">
-        <v>2.618069492969334</v>
+        <v>2.616627627493123</v>
       </c>
       <c r="N7" t="n">
-        <v>12.79393736130389</v>
+        <v>12.75210989992955</v>
       </c>
       <c r="O7" t="n">
-        <v>3.576861384133286</v>
+        <v>3.571009647134763</v>
       </c>
       <c r="P7" t="n">
-        <v>365.9300492369431</v>
+        <v>365.9637222050582</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30279,28 +30463,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02212666280550101</v>
+        <v>-0.02628200229261314</v>
       </c>
       <c r="J8" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K8" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001509346586901161</v>
+        <v>0.002150313030519935</v>
       </c>
       <c r="M8" t="n">
-        <v>3.206987329502361</v>
+        <v>3.206685300664933</v>
       </c>
       <c r="N8" t="n">
-        <v>17.70852416332872</v>
+        <v>17.6644916776848</v>
       </c>
       <c r="O8" t="n">
-        <v>4.208149731571908</v>
+        <v>4.202914664573241</v>
       </c>
       <c r="P8" t="n">
-        <v>369.6226221006154</v>
+        <v>369.6668601842927</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30357,28 +30541,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02635688746421634</v>
+        <v>0.02431024891227678</v>
       </c>
       <c r="J9" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K9" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001827645369851361</v>
+        <v>0.001576110042298517</v>
       </c>
       <c r="M9" t="n">
-        <v>3.400668341480368</v>
+        <v>3.388784706126791</v>
       </c>
       <c r="N9" t="n">
-        <v>20.74423185616315</v>
+        <v>20.63136902472336</v>
       </c>
       <c r="O9" t="n">
-        <v>4.554583609526029</v>
+        <v>4.5421766835652</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9539413205054</v>
+        <v>368.9757350163223</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30416,7 +30600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J632"/>
+  <dimension ref="A1:J636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63263,6 +63447,214 @@
         </is>
       </c>
     </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-36.49461007371047,174.74301666014432</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-36.49509844163899,174.7423549631288</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-36.49555061562469,174.74164211156858</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-36.496104172043644,174.74105421526815</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-36.49672992522533,174.7405914941726</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>-36.49739848122158,174.74027164836502</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>-36.498088301650846,174.74004642468375</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>-36.49880184721019,174.73994700392308</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-36.494594897713355,174.74299933673186</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-36.495087506923845,174.74234248117037</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-36.495544699669125,174.74163444593168</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-36.49609856890133,174.7410456153137</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-36.49672669518817,174.7405845236314</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>-36.49739707061888,174.74026646524388</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>-36.4980873096248,174.74004029553143</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>-36.498801198693066,174.73994080459</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-36.49457322717999,174.74297459981838</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-36.4950743852638,174.7423275028249</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-36.495541586008095,174.7416304113864</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-36.49609851230393,174.74104552844548</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-36.496723554873874,174.74057774671687</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>-36.497397214557935,174.74026699413378</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>-36.49808660103456,174.7400359175656</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>-36.49880070072433,174.73993604438786</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-36.494556924573224,174.74295599040636</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-36.49506199258301,174.7423133566144</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-36.49553822325402,174.74162605407787</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-36.49609528625199,174.74104057695715</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-36.49672189499328,174.74057416463367</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>-36.49739761758731,174.74026847502552</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>-36.49808645931649,174.74003504197242</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>-36.498800225916746,174.7399315055905</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J636"/>
+  <dimension ref="A1:J639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23330,6 +23330,114 @@
       <c r="J636" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>339.58</v>
+      </c>
+      <c r="C637" t="n">
+        <v>343.05</v>
+      </c>
+      <c r="D637" t="n">
+        <v>345.52</v>
+      </c>
+      <c r="E637" t="n">
+        <v>347.7</v>
+      </c>
+      <c r="F637" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="G637" t="n">
+        <v>364.64</v>
+      </c>
+      <c r="H637" t="n">
+        <v>365.47</v>
+      </c>
+      <c r="I637" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>335.16</v>
+      </c>
+      <c r="C638" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="D638" t="n">
+        <v>346.46</v>
+      </c>
+      <c r="E638" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="F638" t="n">
+        <v>360.77</v>
+      </c>
+      <c r="G638" t="n">
+        <v>364.94</v>
+      </c>
+      <c r="H638" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="I638" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>335.16</v>
+      </c>
+      <c r="C639" t="n">
+        <v>343.14</v>
+      </c>
+      <c r="D639" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="E639" t="n">
+        <v>348.04</v>
+      </c>
+      <c r="F639" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="G639" t="n">
+        <v>365.31</v>
+      </c>
+      <c r="H639" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="I639" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23344,7 +23452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B648"/>
+  <dimension ref="A1:B651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29827,6 +29935,36 @@
       </c>
       <c r="B648" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
@@ -29995,28 +30133,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.263095707597757</v>
+        <v>-0.2710414979637037</v>
       </c>
       <c r="J2" t="n">
+        <v>638</v>
+      </c>
+      <c r="K2" t="n">
         <v>635</v>
       </c>
-      <c r="K2" t="n">
-        <v>632</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02672647386977556</v>
+        <v>0.02854128251049948</v>
       </c>
       <c r="M2" t="n">
-        <v>10.35580292915879</v>
+        <v>10.35019659727885</v>
       </c>
       <c r="N2" t="n">
-        <v>139.4607501932479</v>
+        <v>139.1525966241944</v>
       </c>
       <c r="O2" t="n">
-        <v>11.80935011731162</v>
+        <v>11.79629588575136</v>
       </c>
       <c r="P2" t="n">
-        <v>352.1088172265488</v>
+        <v>352.1936665402262</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30073,28 +30211,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3830516342240334</v>
+        <v>-0.3866979734326655</v>
       </c>
       <c r="J3" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K3" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L3" t="n">
-        <v>0.13559725363151</v>
+        <v>0.1389343383562653</v>
       </c>
       <c r="M3" t="n">
-        <v>6.074160982956466</v>
+        <v>6.06683340090451</v>
       </c>
       <c r="N3" t="n">
-        <v>51.61404948183907</v>
+        <v>51.44085164595166</v>
       </c>
       <c r="O3" t="n">
-        <v>7.184291856671684</v>
+        <v>7.172227802151272</v>
       </c>
       <c r="P3" t="n">
-        <v>357.4732696218333</v>
+        <v>357.5122332345733</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30151,28 +30289,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1520432177786217</v>
+        <v>-0.1571837983119384</v>
       </c>
       <c r="J4" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K4" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06161900061929859</v>
+        <v>0.06579013787203336</v>
       </c>
       <c r="M4" t="n">
-        <v>3.342238895596934</v>
+        <v>3.351524084890551</v>
       </c>
       <c r="N4" t="n">
-        <v>19.42614874838375</v>
+        <v>19.47318071775074</v>
       </c>
       <c r="O4" t="n">
-        <v>4.407510493281185</v>
+        <v>4.412842702584213</v>
       </c>
       <c r="P4" t="n">
-        <v>355.6005556683036</v>
+        <v>355.6554849809159</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30229,28 +30367,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2944851390546526</v>
+        <v>-0.2974065026861988</v>
       </c>
       <c r="J5" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K5" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2497191605575398</v>
+        <v>0.2548510896855261</v>
       </c>
       <c r="M5" t="n">
-        <v>2.816779942110757</v>
+        <v>2.817511661295284</v>
       </c>
       <c r="N5" t="n">
-        <v>14.35884687231257</v>
+        <v>14.33619588565415</v>
       </c>
       <c r="O5" t="n">
-        <v>3.789306911865621</v>
+        <v>3.786316928844461</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0541153495346</v>
+        <v>359.0853426255493</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30307,28 +30445,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005243455151492933</v>
+        <v>0.0005519284697417486</v>
       </c>
       <c r="J6" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K6" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001628247127638538</v>
+        <v>1.801198265205528e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.238528954533635</v>
+        <v>2.252962920179158</v>
       </c>
       <c r="N6" t="n">
-        <v>9.303896771297808</v>
+        <v>9.375182305552153</v>
       </c>
       <c r="O6" t="n">
-        <v>3.050228970306624</v>
+        <v>3.061891948706249</v>
       </c>
       <c r="P6" t="n">
-        <v>365.2168201187923</v>
+        <v>365.2669704737131</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30385,28 +30523,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02396565625825717</v>
+        <v>0.02241542313772934</v>
       </c>
       <c r="J7" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K7" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002475943846454443</v>
+        <v>0.002187480296413247</v>
       </c>
       <c r="M7" t="n">
-        <v>2.616627627493123</v>
+        <v>2.611830452290919</v>
       </c>
       <c r="N7" t="n">
-        <v>12.75210989992955</v>
+        <v>12.7050129658673</v>
       </c>
       <c r="O7" t="n">
-        <v>3.571009647134763</v>
+        <v>3.564409202920913</v>
       </c>
       <c r="P7" t="n">
-        <v>365.9637222050582</v>
+        <v>365.9802920529215</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30463,28 +30601,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02628200229261314</v>
+        <v>-0.02907920234351079</v>
       </c>
       <c r="J8" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K8" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002150313030519935</v>
+        <v>0.002652843831293161</v>
       </c>
       <c r="M8" t="n">
-        <v>3.206685300664933</v>
+        <v>3.205022607408297</v>
       </c>
       <c r="N8" t="n">
-        <v>17.6644916776848</v>
+        <v>17.62284732315338</v>
       </c>
       <c r="O8" t="n">
-        <v>4.202914664573241</v>
+        <v>4.197957518026281</v>
       </c>
       <c r="P8" t="n">
-        <v>369.6668601842927</v>
+        <v>369.6967590745633</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30541,28 +30679,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02431024891227678</v>
+        <v>0.02250493836160353</v>
       </c>
       <c r="J9" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K9" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001576110042298517</v>
+        <v>0.001364256606051772</v>
       </c>
       <c r="M9" t="n">
-        <v>3.388784706126791</v>
+        <v>3.381285124180285</v>
       </c>
       <c r="N9" t="n">
-        <v>20.63136902472336</v>
+        <v>20.55148115684107</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5421766835652</v>
+        <v>4.533374147016885</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9757350163223</v>
+        <v>368.9950319141713</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30600,7 +30738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J636"/>
+  <dimension ref="A1:J639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63655,6 +63793,162 @@
         </is>
       </c>
     </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-36.494510004858114,174.74290243165441</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-36.49501573539472,174.74226055422162</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-36.495520350835946,174.7416028957962</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-36.496086004276776,174.74102633057186</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-36.49672288194932,174.74057629452096</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>-36.497398999402094,174.74027355236873</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>-36.4980866718936,174.74003635536215</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>-36.49880031856215,174.7399323912095</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-36.49448071315832,174.74286899529133</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-36.49502097080842,174.7422665304205</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-36.49552620452045,174.74161048073745</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-36.496090305680156,174.74103293255484</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-36.49672440724494,174.74057958616504</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-36.497399863036236,174.74027672570836</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>-36.498087858782114,174.74004368845505</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>-36.498800677563,174.7399358229831</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-36.49448071315832,174.74286899529133</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-36.495016331834265,174.74226123505434</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-36.49552489678246,174.7416087862292</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-36.49608792858886,174.74102928409047</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-36.49672072859065,174.74057164749425</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-36.497400928184895,174.74028063949396</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>-36.49808828393611,174.74004631523462</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>-36.49880083969237,174.73993737281634</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
